--- a/business_forms/043_creative_project_request_form--business_forms.xlsx
+++ b/business_forms/043_creative_project_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>project_type_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>Project Type 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_details</t>
+          <t>project_details_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project Details</t>
+          <t>Project Details 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project_manager_notes</t>
+          <t>project_manager_notes_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Project Manager Notes</t>
+          <t>Project Manager Notes 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>project_manager</t>
+          <t>project_manager_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>project_deadline</t>
+          <t>project_deadline_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Project Deadline</t>
+          <t>Project Deadline 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1103,51 +1103,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>project_type_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project_type_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_type_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
